--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
@@ -566,11 +566,6 @@
           <t>236</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 17A, 17B, 18, 19, 20, 21, 22, 23, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -578,11 +573,6 @@
           <t>237</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3, 4, 5, 6, 7A1, 7A2, 7A3, 7A4, 7A5, 7B1, 7B2, 8A, 8B, 8C, 9</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -590,11 +580,6 @@
           <t>238</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16A, 16B, 16C, 17A, 17B1, 17B2, 2A, 2B, 2C, 2D, 3A, 3B, 3C, 3D, 4, 5A1, 5A2, 5B, 6, 7, 8A1, 8A2, 8B, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -602,11 +587,6 @@
           <t>239</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -614,11 +594,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 18, 19, 2, 20, 3, 4, 5A, 5B, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -626,11 +601,6 @@
           <t>241</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C, 3D, 4, 5A, 5B, 5C, 5D, 6A, 6B, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -638,11 +608,6 @@
           <t>242</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 10C, 11A, 11B, 12, 13A, 13B, 13C, 2, 3, 4, 5A, 5B, 5C, 6B, 7A, 7B, 7C, 7D, 7E, 7F, 7G, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -650,11 +615,6 @@
           <t>243</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -662,11 +622,6 @@
           <t>244</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -674,11 +629,6 @@
           <t>245</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -686,11 +636,6 @@
           <t>246</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -698,11 +643,6 @@
           <t>247</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -710,11 +650,6 @@
           <t>248</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -722,11 +657,6 @@
           <t>249</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -734,11 +664,6 @@
           <t>250</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15A1, 15A2, 15B1, 15B2, 16A1, 16A2, 16B, 17, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -746,11 +671,6 @@
           <t>251</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -758,11 +678,6 @@
           <t>252</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -770,11 +685,6 @@
           <t>253</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 15A, 15B, 1A1, 1A2, 1B, 1C1, 1C2, 2, 3, 4A, 4B, 5, 6A, 6B, 6C, 7A, 7B, 7C, 8A, 8B, 8C, 9</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -782,11 +692,6 @@
           <t>254</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13A, 13B, 14A, 14B, 14C, 15, 16, 17A, 17B, 17C, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 8A, 8B, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -794,11 +699,6 @@
           <t>255</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 2D, 3, 4, 5, 6A, 6B</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -806,11 +706,6 @@
           <t>256</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1A, 1B1A, 1B1B, 1B2, 1C1, 1C2, 1C3, 2A, 2B, 2C, 2D, 3, 4A, 4B, 5A, 5B, 5C, 5D1, 5D2, 5D3, 6A, 6B, 6C, 6D, 6E1, 6E2, 6F1, 6F2, 7A, 7B, 7C, 7D</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -818,11 +713,6 @@
           <t>257</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>10A, 10B1, 10B2, 10B3, 10B4, 11A, 11B1, 11B2, 11B3, 11B4, 12A, 12B, 13, 14, 1A, 1B, 1C, 1D, 2, 3, 4, 5A, 5B, 6A, 6B, 7, 8A, 8B1, 8B2, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -830,11 +720,6 @@
           <t>258</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -842,11 +727,6 @@
           <t>259</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -854,11 +734,6 @@
           <t>260</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 17, 18A, 18B, 19, 2, 3, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -866,11 +741,6 @@
           <t>261</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 18, 19A, 19B, 1A1, 1A2, 1A3, 1A4, 1A5, 1A6, 1B, 2, 20, 21A, 21B, 22, 23A, 23B, 24, 25, 26, 27A, 27B, 3, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -878,11 +748,6 @@
           <t>262</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>10, 11A, 11B, 12, 13, 14A, 14B, 15A, 15B, 1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 3A, 3B, 4A, 4B, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -890,11 +755,6 @@
           <t>263</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11A, 11B, 12A, 12B1, 12B2, 2A1A, 2A1B, 2A1C, 2A2, 2B1, 2B2A, 2B2B, 3A, 3B, 3C, 4, 5A, 5B, 6A1, 6A2, 6B, 7A1, 7A2, 7A3, 7B, 7C, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -902,11 +762,6 @@
           <t>264</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14A, 14B, 15, 16, 1A, 1B, 2, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9A, 9B, 9C1, 9C2</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -914,11 +769,6 @@
           <t>265</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11A, 11B, 11C, 12, 2, 3, 4A, 4B, 5A, 5B, 5C, 6, 7A, 7B1, 7B2, 7C, 7D, 7E, 7F, 7G, 7H, 7I, 8A, 8B, 9A, 9B, 9C</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -926,11 +776,6 @@
           <t>266</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -938,11 +783,6 @@
           <t>267</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -950,11 +790,6 @@
           <t>268</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 17, 1A, 1B, 1C, 1D, 2A, 2B, 3, 4A, 4B, 4C, 4D, 5A, 5B, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -962,11 +797,6 @@
           <t>269</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 13E, 13F, 14, 15A, 15B, 16A, 16B, 17A, 17B, 18, 19A, 19B, 19C, 19D, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -974,11 +804,6 @@
           <t>270</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>10A, 10B, 10C, 10D, 11A, 11B, 12A, 12B, 12C, 13, 14, 15, 16, 1A, 1B, 2A, 2B, 3A, 3B, 4, 5A, 5B, 5C, 5D, 5E, 5F, 5G, 5H, 5I, 5J, 6A, 6B, 6C, 7, 8A, 8B, 8C, 9A, 9B, 9C, 9D, 9E, 9F</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -986,11 +811,6 @@
           <t>271</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -998,11 +818,6 @@
           <t>272</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A, 6B, 7</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1010,11 +825,6 @@
           <t>273</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>10A1A1, 10A1B, 10A2, 10B, 11A, 11B, 11C1, 11C2, 12A, 12B, 13, 14, 15, 16A, 16B, 17, 18, 19A, 19B, 1A1, 1A2, 1B1, 1B2, 1B3, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1, 2A2, 2B, 30, 31, 32, 33A, 33B, 33C, 33D, 34, 35, 36A, 36B, 37A, 37B, 38, 39, 3A, 3B, 3C1, 3C2, 3D1, 3D2, 3E, 3F, 3G, 40, 41, 42, 43, 44, 4A, 4B, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 6F, 7, 8, 9A1A, 9A1B, 9A2, 9B, 9C</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1022,11 +832,6 @@
           <t>274</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1034,11 +839,6 @@
           <t>275</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B1, 13B2, 13C, 14, 15, 16, 17, 18, 19A, 19B, 20, 21, 22A1, 22A10, 22A11, 22A2, 22A3, 22A4, 22A5, 22A6, 22A7, 22A8, 22A9, 22B, 23, 24, 25, 26, 27, 2A, 2B, 2C, 3A1, 3A2, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1046,11 +846,6 @@
           <t>276</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18A, 18B, 19A, 19B, 19C, 20, 21A, 21B, 22, 23, 24, 25, 26A, 26B, 27, 28, 29, 2A, 2B, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1058,11 +853,6 @@
           <t>277</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 13E, 14A, 14B, 15A, 15B, 16A, 16B, 17, 18A, 18B, 19A, 19B, 19C, 2, 20, 21, 22, 23A, 23B, 23C, 24A, 24B, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33A, 33B, 33C, 34, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1070,11 +860,6 @@
           <t>278</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26A, 26B, 26C, 26D, 27, 3, 4A, 4B, 5, 6, 7A, 7B1, 7B2, 8A, 8B, 8C1, 8C2, 9A, 9B1, 9B2</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1082,11 +867,6 @@
           <t>279</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 18C, 18D, 19A, 19B, 19C, 2, 20, 3, 4A, 4B, 5A, 5B, 5C, 6A, 6B, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1094,11 +874,6 @@
           <t>280</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3, 4, 5, 6, 78A1, 7A, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1106,11 +881,6 @@
           <t>281</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1118,11 +888,6 @@
           <t>282</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 3, 4, 5, 6A, 6B, 6C, 6D, 6E, 7, 8, 9A, 9B1, 9B2</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1130,11 +895,6 @@
           <t>283</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4, 5A, 5B, 6A, 6B, 6C, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1142,11 +902,6 @@
           <t>284</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 1A, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1154,11 +909,6 @@
           <t>285</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1166,11 +916,6 @@
           <t>286</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1178,11 +923,6 @@
           <t>287</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1190,11 +930,6 @@
           <t>288</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 14D, 15A, 15B, 15C, 15D, 15E, 16A, 16B, 17A, 17B, 17C, 17D, 18, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 4H, 4I, 4J, 4K, 5, 6A, 6B, 6C, 6D, 6E1, 6E2, 6F, 7A, 7B, 7C1, 7C2, 7D1, 7D2, 7E1, 7E2, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1202,11 +937,6 @@
           <t>289</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1214,11 +944,6 @@
           <t>290</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1226,11 +951,6 @@
           <t>291</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 12, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 7E, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1238,11 +958,6 @@
           <t>292</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11A1, 11A2, 11A3, 11B1, 11B2, 1A1, 1A2A, 1A2B, 1B1, 1B10A, 1B10B, 1B11, 1B12, 1B2, 1B3A, 1B3B, 1B4, 1B5, 1B6, 1B7, 1B8, 1B9, 1C1, 1C2, 1C3, 1C4A, 1C4B, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 3A, 3B, 4A, 4B, 4C, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1250,11 +965,6 @@
           <t>293</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15A, 15B, 16A, 16B, 16C, 17A, 17B, 17C, 17D, 17E, 17F, 18, 19, 1A, 1B, 20, 21, 22, 23, 24, 25, 26, 27A, 27B, 28, 29A, 29B, 2A, 2B, 30, 31, 32, 33, 34A, 34B, 34C, 3A, 3B, 4A, 4B, 4C, 4D1, 4D2, 4D3, 4E1, 4E2, 4F, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1262,11 +972,6 @@
           <t>294</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1274,11 +979,6 @@
           <t>295</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2A, 2B, 2C, 2D, 2E, 3A, 3B, 4A, 4B, 5A, 5B, 6A, 6B, 7, 8A, 8B1, 8B2, 8B3, 8B4, 9A, 9B, 9C, 9D, 9E</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1286,11 +986,6 @@
           <t>296</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1298,11 +993,6 @@
           <t>297</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1310,11 +1000,6 @@
           <t>298</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1322,11 +1007,6 @@
           <t>299</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1334,11 +1014,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1346,11 +1021,6 @@
           <t>301</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 4C, 5A, 5B, 5C, 6A, 6B, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1358,11 +1028,6 @@
           <t>302</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 2, 3, 4A1, 4A2, 4B1, 4B2, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1370,11 +1035,6 @@
           <t>303</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 13E, 14A, 14B, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1382,11 +1042,6 @@
           <t>304</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1394,11 +1049,6 @@
           <t>305</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 2, 3, 4, 5, 6, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1406,11 +1056,6 @@
           <t>306</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1418,11 +1063,6 @@
           <t>307</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D1, 1D2A, 1D2B, 1E1, 1E2, 2A, 2B, 3A, 3B, 3C, 4A, 4B1, 4B2, 5A, 5B, 6A, 6B, 7A, 7B, 8A, 8B</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1430,11 +1070,6 @@
           <t>308</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1A3, 1B1, 1B2, 1C1, 1C2, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 4A, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1442,11 +1077,6 @@
           <t>309</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1454,11 +1084,6 @@
           <t>310</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1466,11 +1091,6 @@
           <t>311</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3A, 3B, 4, 5A, 5B1, 5B10, 5B11, 5B2, 5B3, 5B4, 5B5, 5B6, 5B7, 5B8, 5B9, 5C1, 5C10, 5C11, 5C12, 5C2, 5C3, 5C4, 5C5, 5C6, 5C7, 5C8, 5C9, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1478,11 +1098,6 @@
           <t>312</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1490,11 +1105,6 @@
           <t>313</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1502,11 +1112,6 @@
           <t>314</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 2A, 2B, 2C, 2D, 3A1A, 3A1B, 3A2, 3B, 4, 5A, 5B, 5C, 5D, 5E, 5F, 5G, 5H, 5I, 5J, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1514,11 +1119,6 @@
           <t>315</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 3, 4A, 4B, 4C, 4D, 5A, 5B, 5C, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1526,11 +1126,6 @@
           <t>316</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>10, 11, 12A, 12B, 13A, 13B, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 2, 20, 21, 22, 23, 24, 25A1, 25A2, 25A3, 25B, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 4A, 4B, 4C, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1538,11 +1133,6 @@
           <t>317</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1550,11 +1140,6 @@
           <t>318</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1562,11 +1147,6 @@
           <t>319</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1574,11 +1154,6 @@
           <t>320</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 3, 4, 5, 6A, 6B, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1586,11 +1161,6 @@
           <t>321</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1598,11 +1168,6 @@
           <t>322</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1610,11 +1175,6 @@
           <t>323</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1622,11 +1182,6 @@
           <t>324</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 1A, 1B, 2A, 2B, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8A, 8B, 8C, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1634,11 +1189,6 @@
           <t>325</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1646,11 +1196,6 @@
           <t>326</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1658,11 +1203,6 @@
           <t>327</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1670,11 +1210,6 @@
           <t>328</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1682,11 +1217,6 @@
           <t>329</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1694,11 +1224,6 @@
           <t>330</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1706,11 +1231,6 @@
           <t>331</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1718,11 +1238,6 @@
           <t>332</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1730,11 +1245,6 @@
           <t>333</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 5</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1742,11 +1252,6 @@
           <t>334</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1754,11 +1259,6 @@
           <t>335</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1766,11 +1266,6 @@
           <t>336</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1778,11 +1273,6 @@
           <t>337</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1790,11 +1280,6 @@
           <t>338</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1802,11 +1287,6 @@
           <t>339</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1814,11 +1294,6 @@
           <t>340</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1826,11 +1301,6 @@
           <t>341</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1838,11 +1308,6 @@
           <t>342</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11, 12A, 12B, 13, 14, 15, 16, 17A, 17B, 18, 19, 1A, 1B, 1C, 1D, 1E, 1F, 2, 20, 3, 4A, 4B, 4C, 5, 6, 7A, 7B, 7C, 7D, 8A1, 8A2, 8B1, 8B2, 9</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1850,11 +1315,6 @@
           <t>343</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 13C, 14, 15, 16, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1862,11 +1322,6 @@
           <t>344</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1874,11 +1329,6 @@
           <t>345</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B1, 2B2, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 2K, 3, 4A, 4B, 5</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1886,11 +1336,6 @@
           <t>346</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 10C, 11, 12, 13, 14, 15A, 15B, 15C, 15D, 16, 17, 18, 19A1, 19A2, 19B, 2, 20, 21, 22, 3, 4, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1898,11 +1343,6 @@
           <t>347</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11, 12A, 12B, 13, 14, 15A, 15B, 15C, 15D, 15E, 15F, 15G, 15H, 15I, 15J, 15K, 16, 17, 18A, 18B1, 18B2, 18C, 18D, 1A, 1B, 1C, 1D1, 1D2, 1E, 1F1, 1F2, 1G, 1H, 1I, 1J, 1K, 2A, 2B, 3, 4, 5A, 5B, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1910,11 +1350,6 @@
           <t>348</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C1, 1C2, 1C3, 1D, 1E, 1F, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1922,11 +1357,6 @@
           <t>349</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21, 22, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 8C, 9</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1934,11 +1364,6 @@
           <t>350</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 35, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1946,11 +1371,6 @@
           <t>351</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 14, 15, 16, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1958,11 +1378,6 @@
           <t>352</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11A, 11B, 12A, 12B, 12C, 12D, 12E, 12F, 12G, 13, 14A, 14B, 14C, 15, 16, 17, 18A, 18B, 18C, 18D, 19A, 19B, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1, 2A2, 2B, 3, 30, 31, 32, 33, 34, 35A, 35B, 36, 37, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1970,11 +1385,6 @@
           <t>353</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18A, 18B, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1982,11 +1392,6 @@
           <t>354</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 15C, 15D, 16A, 16B, 16C, 16D1, 16D2, 16E, 16F, 16G, 16H, 17, 18, 19A, 19B, 19C, 19D, 2, 20, 21, 22, 23A, 23B, 23C, 3, 4, 5, 6A, 6B, 7, 8A, 8B, 8C, 9A, 9B, 9C1, 9C2, 9D, 9E</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1994,11 +1399,6 @@
           <t>355</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2006,11 +1406,6 @@
           <t>356</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25A, 25B, 26, 27, 28, 29, 3, 30, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2018,11 +1413,6 @@
           <t>357</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 4, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2030,11 +1420,6 @@
           <t>358</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 6C, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2042,11 +1427,6 @@
           <t>359</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 21C, 22, 23, 24, 25, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2054,11 +1434,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A1, 17A2, 17B, 18, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2066,11 +1441,6 @@
           <t>361</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2078,11 +1448,6 @@
           <t>362</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2090,11 +1455,6 @@
           <t>363</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2102,11 +1462,6 @@
           <t>364</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 12C, 12D, 12E, 13, 14A, 14B, 14C, 15, 16, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2114,11 +1469,6 @@
           <t>365</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A1, 12A2, 12A3, 12B, 12C1, 12C2, 12C3, 12D, 12E, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 2A, 2B, 3, 4, 5, 6A1, 6A2, 6A3, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2126,11 +1476,6 @@
           <t>366</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12A, 12B, 13, 14A, 14B, 15A, 15B, 16A, 16B, 16C, 16D1, 16D2, 17A, 17B, 17C, 18, 19, 2, 20, 3A, 3B, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 5, 6A, 6B, 7, 8, 9A1, 9A2, 9B, 9C, 9D, 9E, 9F</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2138,11 +1483,6 @@
           <t>367</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 2C, 3, 4, 5A, 5B, 6A, 6B1A1, 6B1A2, 6B1B, 6B2, 6C1, 6C2, 6C3, 6D, 6E1, 6E2, 6F1, 6F2, 6F3, 6F4, 6F5, 6G, 7A, 7B, 7C1, 7C2, 7D</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2150,11 +1490,6 @@
           <t>368</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E1, 1E2, 1E3, 2A, 2B, 2C1, 2C2, 2D1, 2D2, 3A, 3B1, 3B2, 4A1, 4A2, 4B, 4C1, 4C2, 4D, 4E1A1, 4E1A2, 4E1B, 4E2</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2162,11 +1497,6 @@
           <t>369</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B1, 2B2, 2C1, 2C2, 3A, 3B, 4, 5A, 5B, 6A, 6B, 7A, 7B, 7C</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2174,11 +1504,6 @@
           <t>370</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 3A1, 3A2, 3A3, 3A4, 3A5, 3A6, 3B, 4A, 4B, 5A, 5B, 5C, 5D, 5E, 6A1, 6A2, 6B, 7A1, 7A2, 7B1, 7B2, 8A, 8B</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2186,11 +1511,6 @@
           <t>371</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 2, 3A, 3B, 3C, 4, 5, 6A1A1, 6A1A2, 6A1B, 6A2, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2198,11 +1518,6 @@
           <t>372</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>10A1, 10A2, 10B, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2210,11 +1525,6 @@
           <t>373</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2222,11 +1532,6 @@
           <t>374</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 2A, 2B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2234,11 +1539,6 @@
           <t>375</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9A, 9B1, 9B2</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2246,11 +1546,6 @@
           <t>376</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2258,11 +1553,6 @@
           <t>377</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2270,11 +1560,6 @@
           <t>378</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22A, 22B, 23, 24, 25, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 4, 5A, 5B, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2282,11 +1567,6 @@
           <t>379</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 3, 4, 5A, 5B, 6, 7, 8, 9A, 9B, 9C, 9D</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2294,11 +1574,6 @@
           <t>380</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2306,11 +1581,6 @@
           <t>381</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2318,11 +1588,6 @@
           <t>382</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2A, 2B, 2C, 3A, 3B, 3C, 4A, 4B, 4C, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2330,11 +1595,6 @@
           <t>383</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2342,11 +1602,6 @@
           <t>384</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 3A, 3B, 3C1, 3C2, 3C3</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2354,11 +1609,6 @@
           <t>385</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18A, 18B, 19, 2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2366,11 +1616,6 @@
           <t>386</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2378,11 +1623,6 @@
           <t>387</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 19, 2, 20A, 20B, 20C, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2390,11 +1630,6 @@
           <t>388</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2402,11 +1637,6 @@
           <t>389</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2414,11 +1644,6 @@
           <t>390</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24A, 24B, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2426,11 +1651,6 @@
           <t>391</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>10, 11A, 11B, 11C, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2438,11 +1658,6 @@
           <t>392</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2450,11 +1665,6 @@
           <t>393</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2462,11 +1672,6 @@
           <t>394</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>10, 11, 12A, 12B, 12C, 12D, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 23, 24, 25, 26A, 26B, 26C, 27A, 27B, 27C, 27D, 28, 29, 2A, 2B, 30, 31, 32, 33, 34, 35, 36, 37, 3A, 3B, 3C, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2474,11 +1679,6 @@
           <t>395</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 14, 15A, 15B, 16A, 16B, 16C, 17, 18A, 18B, 19A, 19B, 19C, 2, 20A, 20B, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2486,11 +1686,6 @@
           <t>396</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2498,11 +1693,6 @@
           <t>397</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2510,11 +1700,6 @@
           <t>398</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A1, 4A2, 4B1, 4B2, 4B3, 5</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2522,11 +1707,6 @@
           <t>399</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2A1A1, 2A1A2, 2A1A3, 2A1B, 2A2A, 2A2B, 2A2C, 2A2D1, 2A2D2, 2B, 3A1, 3A2, 3A3, 3A4A, 3A4B, 3A4C, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2534,11 +1714,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 2, 3A, 3B, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2546,11 +1721,6 @@
           <t>401</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B1, 3B2, 3B3, 3B4, 3B5</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2558,11 +1728,6 @@
           <t>402</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2570,11 +1735,6 @@
           <t>403</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2582,11 +1742,6 @@
           <t>404</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2594,11 +1749,6 @@
           <t>405</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 1A, 1B1, 1B2, 1B3, 2A, 2B, 2C, 3A, 3B, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2606,11 +1756,6 @@
           <t>406</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2618,11 +1763,6 @@
           <t>407</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17A, 17B, 17C, 17D, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2630,11 +1770,6 @@
           <t>408</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 12C, 12D, 13, 14, 2, 3, 4A1, 4A2, 4B1, 4B2, 5, 6A, 6B, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2642,11 +1777,6 @@
           <t>409</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A1A1, 14A2, 14B1A1, 14B2, 15, 16A, 16B, 17A, 17B, 18, 19, 2A, 2B, 3A, 3B, 4, 5, 6, 7A, 7B, 7C1, 7C2, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2654,11 +1784,6 @@
           <t>410</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11A, 11B, 12A, 12B, 13, 14, 16, 17A, 18, 19, 2A1, 2A2, 2B, 3A, 3B1, 3B2, 3B3, 3C1A1, 3C1A2, 3C1A3, 3C1B, 3C2, 3D1A, 3D1A2, 3D1B, 3D2, 4A, 4B, 5A, 5B, 6, 7, 8, 9A1, 9A2, 9B1, 9B2, 9C1A, 9C1B, 9C2</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2666,11 +1791,6 @@
           <t>411</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2678,11 +1798,6 @@
           <t>412</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D1, 1D2A, 1D2B, 2A, 2B, 2C, 2D, 2E</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2690,11 +1805,6 @@
           <t>413</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2702,11 +1812,6 @@
           <t>414</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2714,11 +1819,6 @@
           <t>415</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C, 3D, 3E, 4</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2726,11 +1826,6 @@
           <t>416</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>1, 10, 11A1, 11A2, 11B, 11C, 12A1, 12A2A, 12A2B, 12B1, 12B2A, 12B2B, 12B2C, 13A, 13B, 14A1A1A1, 14A1B, 14A2, 14B, 15A, 15B, 16A, 16B1, 16B2, 16C, 17, 18, 19, 2, 20, 21A, 21B, 22A1, 22A2, 22B, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A, 3B, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 5A1A, 5A1B, 5A2, 5B1, 5B2, 5C1, 5C2, 60, 61, 62, 63, 64, 6A1, 6A2, 6B1A1, 6B2, 6B3, 6B4, 6B5A1, 7A1, 7A2, 7B1A1A, 7B2A1, 7B2A2, 7B3, 8A1, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2738,11 +1833,6 @@
           <t>417</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 2A, 2B, 2C, 2D, 3A, 3B, 3C, 4A1A1A1A, 4A1B, 4A2A1, 4A2B, 4A3A, 4A3B, 4B, 5A1A, 5A2A, 5A2B, 5A3, 5B1, 5B2A, 5B2B, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2750,11 +1840,6 @@
           <t>418</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>1, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3A, 3B, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2762,11 +1847,6 @@
           <t>419</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2774,11 +1854,6 @@
           <t>420</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1A3A1, 1A3A2, 1A3B, 1A4A1, 1A4A2, 1A4B, 1B1, 1B2, 1B3A, 1B3B, 1B3C, 1B4, 1B5A, 1B5B, 1C1, 1C2, 2A, 2B, 3A1, 3A2, 3B1A, 3B1B, 3B2, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2786,11 +1861,6 @@
           <t>421</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 1B, 29, 2A, 2B1A, 2B1B, 2B2, 2C, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 6, 7, 9</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2798,11 +1868,6 @@
           <t>422</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5A, 5B1, 5B2, 6A, 6B, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2810,11 +1875,6 @@
           <t>423</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2822,11 +1882,6 @@
           <t>424</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2834,11 +1889,6 @@
           <t>425</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2846,21 +1896,11 @@
           <t>426</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B1, 14B2, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
           <t>427</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A, 6B, 7, 8A, 8B</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
@@ -566,6 +566,11 @@
           <t>236</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 17A, 17B, 18, 19, 20, 21, 22, 23, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -573,6 +578,11 @@
           <t>237</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7A1, 7A2, 7A3, 7A4, 7A5, 7B1, 7B2, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -580,6 +590,11 @@
           <t>238</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16A, 16B, 16C, 17A, 17B1, 17B2, 2A, 2B, 2C, 2D, 3A, 3B, 3C, 3D, 4, 5A1, 5A2, 5B, 6, 7, 8A1, 8A2, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -587,6 +602,11 @@
           <t>239</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -594,6 +614,11 @@
           <t>240</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 18, 19, 2, 20, 3, 4, 5A, 5B, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -601,6 +626,11 @@
           <t>241</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 4, 5A, 5B, 5C, 5D, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -608,6 +638,11 @@
           <t>242</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 11A, 11B, 12, 13A, 13B, 13C, 2, 3, 4, 5A, 5B, 5C, 6B, 7A, 7B, 7C, 7D, 7E, 7F, 7G, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -615,6 +650,11 @@
           <t>243</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -622,6 +662,11 @@
           <t>244</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -629,6 +674,11 @@
           <t>245</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -636,6 +686,11 @@
           <t>246</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -643,6 +698,11 @@
           <t>247</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -650,6 +710,11 @@
           <t>248</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -657,6 +722,11 @@
           <t>249</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -664,6 +734,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15A1, 15A2, 15B1, 15B2, 16A1, 16A2, 16B, 17, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -671,6 +746,11 @@
           <t>251</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -678,6 +758,11 @@
           <t>252</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -685,6 +770,11 @@
           <t>253</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 15A, 15B, 1A1, 1A2, 1B, 1C1, 1C2, 2, 3, 4A, 4B, 5, 6A, 6B, 6C, 7A, 7B, 7C, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -692,6 +782,11 @@
           <t>254</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13A, 13B, 14A, 14B, 14C, 15, 16, 17A, 17B, 17C, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -699,6 +794,11 @@
           <t>255</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 3, 4, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -706,6 +806,11 @@
           <t>256</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1A, 1B1A, 1B1B, 1B2, 1C1, 1C2, 1C3, 2A, 2B, 2C, 2D, 3, 4A, 4B, 5A, 5B, 5C, 5D1, 5D2, 5D3, 6A, 6B, 6C, 6D, 6E1, 6E2, 6F1, 6F2, 7A, 7B, 7C, 7D</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -713,6 +818,11 @@
           <t>257</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10A, 10B1, 10B2, 10B3, 10B4, 11A, 11B1, 11B2, 11B3, 11B4, 12A, 12B, 13, 14, 1A, 1B, 1C, 1D, 2, 3, 4, 5A, 5B, 6A, 6B, 7, 8A, 8B1, 8B2, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -720,6 +830,11 @@
           <t>258</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -727,6 +842,11 @@
           <t>259</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -734,6 +854,11 @@
           <t>260</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 17, 18A, 18B, 19, 2, 3, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -741,6 +866,11 @@
           <t>261</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 18, 19A, 19B, 1A1, 1A2, 1A3, 1A4, 1A5, 1A6, 1B, 2, 20, 21A, 21B, 22, 23A, 23B, 24, 25, 26, 27A, 27B, 3, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -748,6 +878,11 @@
           <t>262</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 14A, 14B, 15A, 15B, 1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 3A, 3B, 4A, 4B, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -755,6 +890,11 @@
           <t>263</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11A, 11B, 12A, 12B1, 12B2, 2A1A, 2A1B, 2A1C, 2A2, 2B1, 2B2A, 2B2B, 3A, 3B, 3C, 4, 5A, 5B, 6A1, 6A2, 6B, 7A1, 7A2, 7A3, 7B, 7C, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -762,6 +902,11 @@
           <t>264</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14A, 14B, 15, 16, 1A, 1B, 2, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9A, 9B, 9C1, 9C2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -769,6 +914,11 @@
           <t>265</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11A, 11B, 11C, 12, 2, 3, 4A, 4B, 5A, 5B, 5C, 6, 7A, 7B1, 7B2, 7C, 7D, 7E, 7F, 7G, 7H, 7I, 8A, 8B, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -776,6 +926,11 @@
           <t>266</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -783,6 +938,11 @@
           <t>267</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -790,6 +950,11 @@
           <t>268</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 17, 1A, 1B, 1C, 1D, 2A, 2B, 3, 4A, 4B, 4C, 4D, 5A, 5B, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -797,6 +962,11 @@
           <t>269</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 13E, 13F, 14, 15A, 15B, 16A, 16B, 17A, 17B, 18, 19A, 19B, 19C, 19D, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -804,6 +974,11 @@
           <t>270</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>10A, 10B, 10C, 10D, 11A, 11B, 12A, 12B, 12C, 13, 14, 15, 16, 1A, 1B, 2A, 2B, 3A, 3B, 4, 5A, 5B, 5C, 5D, 5E, 5F, 5G, 5H, 5I, 5J, 6A, 6B, 6C, 7, 8A, 8B, 8C, 9A, 9B, 9C, 9D, 9E, 9F</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -811,6 +986,11 @@
           <t>271</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -818,6 +998,11 @@
           <t>272</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -825,6 +1010,11 @@
           <t>273</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10A1A1, 10A1B, 10A2, 10B, 11A, 11B, 11C1, 11C2, 12A, 12B, 13, 14, 15, 16A, 16B, 17, 18, 19A, 19B, 1A1, 1A2, 1B1, 1B2, 1B3, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1, 2A2, 2B, 30, 31, 32, 33A, 33B, 33C, 33D, 34, 35, 36A, 36B, 37A, 37B, 38, 39, 3A, 3B, 3C1, 3C2, 3D1, 3D2, 3E, 3F, 3G, 40, 41, 42, 43, 44, 4A, 4B, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 6F, 7, 8, 9A1A, 9A1B, 9A2, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -832,6 +1022,11 @@
           <t>274</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -839,6 +1034,11 @@
           <t>275</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B1, 13B2, 13C, 14, 15, 16, 17, 18, 19A, 19B, 20, 21, 22A1, 22A10, 22A11, 22A2, 22A3, 22A4, 22A5, 22A6, 22A7, 22A8, 22A9, 22B, 23, 24, 25, 26, 27, 2A, 2B, 2C, 3A1, 3A2, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -846,6 +1046,11 @@
           <t>276</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18A, 18B, 19A, 19B, 19C, 20, 21A, 21B, 22, 23, 24, 25, 26A, 26B, 27, 28, 29, 2A, 2B, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -853,6 +1058,11 @@
           <t>277</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 13E, 14A, 14B, 15A, 15B, 16A, 16B, 17, 18A, 18B, 19A, 19B, 19C, 2, 20, 21, 22, 23A, 23B, 23C, 24A, 24B, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33A, 33B, 33C, 34, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -860,6 +1070,11 @@
           <t>278</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26A, 26B, 26C, 26D, 27, 3, 4A, 4B, 5, 6, 7A, 7B1, 7B2, 8A, 8B, 8C1, 8C2, 9A, 9B1, 9B2</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -867,6 +1082,11 @@
           <t>279</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 18C, 18D, 19A, 19B, 19C, 2, 20, 3, 4A, 4B, 5A, 5B, 5C, 6A, 6B, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -874,6 +1094,11 @@
           <t>280</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3, 4, 5, 6, 78A1, 7A, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -881,6 +1106,11 @@
           <t>281</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -888,6 +1118,11 @@
           <t>282</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 3, 4, 5, 6A, 6B, 6C, 6D, 6E, 7, 8, 9A, 9B1, 9B2</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -895,6 +1130,11 @@
           <t>283</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5A, 5B, 6A, 6B, 6C, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -902,6 +1142,11 @@
           <t>284</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 1A, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -909,6 +1154,11 @@
           <t>285</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -916,6 +1166,11 @@
           <t>286</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -923,6 +1178,11 @@
           <t>287</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -930,6 +1190,11 @@
           <t>288</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 14D, 15A, 15B, 15C, 15D, 15E, 16A, 16B, 17A, 17B, 17C, 17D, 18, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 4H, 4I, 4J, 4K, 5, 6A, 6B, 6C, 6D, 6E1, 6E2, 6F, 7A, 7B, 7C1, 7C2, 7D1, 7D2, 7E1, 7E2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -937,6 +1202,11 @@
           <t>289</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -944,6 +1214,11 @@
           <t>290</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -951,6 +1226,11 @@
           <t>291</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 12, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 7E, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -958,6 +1238,11 @@
           <t>292</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11A1, 11A2, 11A3, 11B1, 11B2, 1A1, 1A2A, 1A2B, 1B1, 1B10A, 1B10B, 1B11, 1B12, 1B2, 1B3A, 1B3B, 1B4, 1B5, 1B6, 1B7, 1B8, 1B9, 1C1, 1C2, 1C3, 1C4A, 1C4B, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 3A, 3B, 4A, 4B, 4C, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -965,6 +1250,11 @@
           <t>293</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15A, 15B, 16A, 16B, 16C, 17A, 17B, 17C, 17D, 17E, 17F, 18, 19, 1A, 1B, 20, 21, 22, 23, 24, 25, 26, 27A, 27B, 28, 29A, 29B, 2A, 2B, 30, 31, 32, 33, 34A, 34B, 34C, 3A, 3B, 4A, 4B, 4C, 4D1, 4D2, 4D3, 4E1, 4E2, 4F, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -972,6 +1262,11 @@
           <t>294</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -979,6 +1274,11 @@
           <t>295</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2A, 2B, 2C, 2D, 2E, 3A, 3B, 4A, 4B, 5A, 5B, 6A, 6B, 7, 8A, 8B1, 8B2, 8B3, 8B4, 9A, 9B, 9C, 9D, 9E</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -986,6 +1286,11 @@
           <t>296</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -993,6 +1298,11 @@
           <t>297</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1000,6 +1310,11 @@
           <t>298</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1007,6 +1322,11 @@
           <t>299</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1014,6 +1334,11 @@
           <t>300</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1021,6 +1346,11 @@
           <t>301</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 5A, 5B, 5C, 6A, 6B, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1028,6 +1358,11 @@
           <t>302</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 2, 3, 4A1, 4A2, 4B1, 4B2, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1035,6 +1370,11 @@
           <t>303</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 13E, 14A, 14B, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1042,6 +1382,11 @@
           <t>304</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1049,6 +1394,11 @@
           <t>305</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 2, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1056,6 +1406,11 @@
           <t>306</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1063,6 +1418,11 @@
           <t>307</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2A, 1D2B, 1E1, 1E2, 2A, 2B, 3A, 3B, 3C, 4A, 4B1, 4B2, 5A, 5B, 6A, 6B, 7A, 7B, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1070,6 +1430,11 @@
           <t>308</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B1, 1B2, 1C1, 1C2, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1077,6 +1442,11 @@
           <t>309</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1084,6 +1454,11 @@
           <t>310</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1091,6 +1466,11 @@
           <t>311</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3A, 3B, 4, 5A, 5B1, 5B10, 5B11, 5B2, 5B3, 5B4, 5B5, 5B6, 5B7, 5B8, 5B9, 5C1, 5C10, 5C11, 5C12, 5C2, 5C3, 5C4, 5C5, 5C6, 5C7, 5C8, 5C9, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1098,6 +1478,11 @@
           <t>312</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1105,6 +1490,11 @@
           <t>313</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1112,11 +1502,21 @@
           <t>314</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 2A, 2B, 2C, 2D, 3A1A, 3A1B, 3A2, 3B, 4, 5A, 5B, 5C, 5D, 5E, 5F, 5G, 5H, 5I, 5J, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
           <t>315</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 3, 4A, 4B, 4C, 4D, 5A, 5B, 5C, 6, 7A, 7B, 7C, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
@@ -1526,6 +1526,11 @@
           <t>316</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13A, 13B, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 2, 20, 21, 22, 23, 24, 25A1, 25A2, 25A3, 25B, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 4A, 4B, 4C, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1533,6 +1538,11 @@
           <t>317</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1540,6 +1550,11 @@
           <t>318</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1547,6 +1562,11 @@
           <t>319</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1554,6 +1574,11 @@
           <t>320</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 3, 4, 5, 6A, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1561,6 +1586,11 @@
           <t>321</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1568,6 +1598,11 @@
           <t>322</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1575,6 +1610,11 @@
           <t>323</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1582,6 +1622,11 @@
           <t>324</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 1A, 1B, 2A, 2B, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8A, 8B, 8C, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1589,6 +1634,11 @@
           <t>325</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1596,6 +1646,11 @@
           <t>326</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1603,6 +1658,11 @@
           <t>327</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1610,6 +1670,11 @@
           <t>328</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1617,6 +1682,11 @@
           <t>329</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1624,6 +1694,11 @@
           <t>330</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1631,6 +1706,11 @@
           <t>331</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1638,6 +1718,11 @@
           <t>332</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1645,6 +1730,11 @@
           <t>333</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 5</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1652,6 +1742,11 @@
           <t>334</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1659,6 +1754,11 @@
           <t>335</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1666,6 +1766,11 @@
           <t>336</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1673,6 +1778,11 @@
           <t>337</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1680,6 +1790,11 @@
           <t>338</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1687,6 +1802,11 @@
           <t>339</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1694,6 +1814,11 @@
           <t>340</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1701,6 +1826,11 @@
           <t>341</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1708,6 +1838,11 @@
           <t>342</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12A, 12B, 13, 14, 15, 16, 17A, 17B, 18, 19, 1A, 1B, 1C, 1D, 1E, 1F, 2, 20, 3, 4A, 4B, 4C, 5, 6, 7A, 7B, 7C, 7D, 8A1, 8A2, 8B1, 8B2, 9</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1715,6 +1850,11 @@
           <t>343</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 14, 15, 16, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1722,6 +1862,11 @@
           <t>344</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1729,6 +1874,11 @@
           <t>345</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 2K, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1736,6 +1886,11 @@
           <t>346</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 11, 12, 13, 14, 15A, 15B, 15C, 15D, 16, 17, 18, 19A1, 19A2, 19B, 2, 20, 21, 22, 3, 4, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1743,6 +1898,11 @@
           <t>347</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12A, 12B, 13, 14, 15A, 15B, 15C, 15D, 15E, 15F, 15G, 15H, 15I, 15J, 15K, 16, 17, 18A, 18B1, 18B2, 18C, 18D, 1A, 1B, 1C, 1D1, 1D2, 1E, 1F1, 1F2, 1G, 1H, 1I, 1J, 1K, 2A, 2B, 3, 4, 5A, 5B, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1750,6 +1910,11 @@
           <t>348</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C1, 1C2, 1C3, 1D, 1E, 1F, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1757,6 +1922,11 @@
           <t>349</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21, 22, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1764,6 +1934,11 @@
           <t>350</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 35, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1771,6 +1946,11 @@
           <t>351</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 14, 15, 16, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1778,6 +1958,11 @@
           <t>352</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11A, 11B, 12A, 12B, 12C, 12D, 12E, 12F, 12G, 13, 14A, 14B, 14C, 15, 16, 17, 18A, 18B, 18C, 18D, 19A, 19B, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1, 2A2, 2B, 3, 30, 31, 32, 33, 34, 35A, 35B, 36, 37, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1785,6 +1970,11 @@
           <t>353</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18A, 18B, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1792,6 +1982,11 @@
           <t>354</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 15C, 15D, 16A, 16B, 16C, 16D1, 16D2, 16E, 16F, 16G, 16H, 17, 18, 19A, 19B, 19C, 19D, 2, 20, 21, 22, 23A, 23B, 23C, 3, 4, 5, 6A, 6B, 7, 8A, 8B, 8C, 9A, 9B, 9C1, 9C2, 9D, 9E</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1799,6 +1994,11 @@
           <t>355</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1806,6 +2006,11 @@
           <t>356</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25A, 25B, 26, 27, 28, 29, 3, 30, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1813,6 +2018,11 @@
           <t>357</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1820,6 +2030,11 @@
           <t>358</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1827,6 +2042,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 21C, 22, 23, 24, 25, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1834,6 +2054,11 @@
           <t>360</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A1, 17A2, 17B, 18, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1841,6 +2066,11 @@
           <t>361</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1848,6 +2078,11 @@
           <t>362</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1855,6 +2090,11 @@
           <t>363</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1862,6 +2102,11 @@
           <t>364</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 12E, 13, 14A, 14B, 14C, 15, 16, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1869,6 +2114,11 @@
           <t>365</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A1, 12A2, 12A3, 12B, 12C1, 12C2, 12C3, 12D, 12E, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 2A, 2B, 3, 4, 5, 6A1, 6A2, 6A3, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1876,6 +2126,11 @@
           <t>366</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12A, 12B, 13, 14A, 14B, 15A, 15B, 16A, 16B, 16C, 16D1, 16D2, 17A, 17B, 17C, 18, 19, 2, 20, 3A, 3B, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 5, 6A, 6B, 7, 8, 9A1, 9A2, 9B, 9C, 9D, 9E, 9F</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1883,6 +2138,11 @@
           <t>367</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3, 4, 5A, 5B, 6A, 6B1A1, 6B1A2, 6B1B, 6B2, 6C1, 6C2, 6C3, 6D, 6E1, 6E2, 6F1, 6F2, 6F3, 6F4, 6F5, 6G, 7A, 7B, 7C1, 7C2, 7D</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1890,6 +2150,11 @@
           <t>368</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E1, 1E2, 1E3, 2A, 2B, 2C1, 2C2, 2D1, 2D2, 3A, 3B1, 3B2, 4A1, 4A2, 4B, 4C1, 4C2, 4D, 4E1A1, 4E1A2, 4E1B, 4E2</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1897,6 +2162,11 @@
           <t>369</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C1, 2C2, 3A, 3B, 4, 5A, 5B, 6A, 6B, 7A, 7B, 7C</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1904,6 +2174,11 @@
           <t>370</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A1, 3A2, 3A3, 3A4, 3A5, 3A6, 3B, 4A, 4B, 5A, 5B, 5C, 5D, 5E, 6A1, 6A2, 6B, 7A1, 7A2, 7B1, 7B2, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1911,6 +2186,11 @@
           <t>371</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3A, 3B, 3C, 4, 5, 6A1A1, 6A1A2, 6A1B, 6A2, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1918,6 +2198,11 @@
           <t>372</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>10A1, 10A2, 10B, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1925,6 +2210,11 @@
           <t>373</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1932,6 +2222,11 @@
           <t>374</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 2A, 2B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1939,6 +2234,11 @@
           <t>375</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9A, 9B1, 9B2</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1946,6 +2246,11 @@
           <t>376</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1953,6 +2258,11 @@
           <t>377</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1960,6 +2270,11 @@
           <t>378</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22A, 22B, 23, 24, 25, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 4, 5A, 5B, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -1967,6 +2282,11 @@
           <t>379</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 3, 4, 5A, 5B, 6, 7, 8, 9A, 9B, 9C, 9D</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -1974,6 +2294,11 @@
           <t>380</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -1981,6 +2306,11 @@
           <t>381</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -1988,6 +2318,11 @@
           <t>382</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2A, 2B, 2C, 3A, 3B, 3C, 4A, 4B, 4C, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -1995,6 +2330,11 @@
           <t>383</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2002,6 +2342,11 @@
           <t>384</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 3A, 3B, 3C1, 3C2, 3C3</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2009,6 +2354,11 @@
           <t>385</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18A, 18B, 19, 2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2016,6 +2366,11 @@
           <t>386</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2023,6 +2378,11 @@
           <t>387</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 19, 2, 20A, 20B, 20C, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2030,6 +2390,11 @@
           <t>388</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2037,6 +2402,11 @@
           <t>389</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2044,6 +2414,11 @@
           <t>390</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24A, 24B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2051,6 +2426,11 @@
           <t>391</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 11C, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2058,6 +2438,11 @@
           <t>392</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2065,6 +2450,11 @@
           <t>393</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2072,6 +2462,11 @@
           <t>394</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 12C, 12D, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 23, 24, 25, 26A, 26B, 26C, 27A, 27B, 27C, 27D, 28, 29, 2A, 2B, 30, 31, 32, 33, 34, 35, 36, 37, 3A, 3B, 3C, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2079,6 +2474,11 @@
           <t>395</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 14, 15A, 15B, 16A, 16B, 16C, 17, 18A, 18B, 19A, 19B, 19C, 2, 20A, 20B, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2086,6 +2486,11 @@
           <t>396</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2093,6 +2498,11 @@
           <t>397</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2100,6 +2510,11 @@
           <t>398</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1, 4A2, 4B1, 4B2, 4B3, 5</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2107,6 +2522,11 @@
           <t>399</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A1A1, 2A1A2, 2A1A3, 2A1B, 2A2A, 2A2B, 2A2C, 2A2D1, 2A2D2, 2B, 3A1, 3A2, 3A3, 3A4A, 3A4B, 3A4C, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2114,6 +2534,11 @@
           <t>400</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 2, 3A, 3B, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2121,6 +2546,11 @@
           <t>401</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B1, 3B2, 3B3, 3B4, 3B5</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2128,6 +2558,11 @@
           <t>402</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2135,6 +2570,11 @@
           <t>403</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2142,6 +2582,11 @@
           <t>404</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2149,11 +2594,21 @@
           <t>405</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 1A, 1B1, 1B2, 1B3, 2A, 2B, 2C, 3A, 3B, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
           <t>406</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
@@ -1214,6 +1214,11 @@
           <t>290</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1221,6 +1226,11 @@
           <t>291</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 12, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 7E, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1228,6 +1238,11 @@
           <t>292</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11A1, 11A2, 11A3, 11B1, 11B2, 1A1, 1A2A, 1A2B, 1B1, 1B10A, 1B10B, 1B11, 1B12, 1B2, 1B3A, 1B3B, 1B4, 1B5, 1B6, 1B7, 1B8, 1B9, 1C1, 1C2, 1C3, 1C4A, 1C4B, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 3A, 3B, 4A, 4B, 4C, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1235,6 +1250,11 @@
           <t>293</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15A, 15B, 16A, 16B, 16C, 17A, 17B, 17C, 17D, 17E, 17F, 18, 19, 1A, 1B, 20, 21, 22, 23, 24, 25, 26, 27A, 27B, 28, 29A, 29B, 2A, 2B, 30, 31, 32, 33, 34A, 34B, 34C, 3A, 3B, 4A, 4B, 4C, 4D1, 4D2, 4D3, 4E1, 4E2, 4F, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1242,6 +1262,11 @@
           <t>294</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1249,6 +1274,11 @@
           <t>295</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2A, 2B, 2C, 2D, 2E, 3A, 3B, 4A, 4B, 5A, 5B, 6A, 6B, 7, 8A, 8B1, 8B2, 8B3, 8B4, 9A, 9B, 9C, 9D, 9E</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1256,6 +1286,11 @@
           <t>296</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1263,6 +1298,11 @@
           <t>297</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1270,6 +1310,11 @@
           <t>298</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1277,6 +1322,11 @@
           <t>299</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1284,6 +1334,11 @@
           <t>300</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1291,6 +1346,11 @@
           <t>301</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 5A, 5B, 5C, 6A, 6B, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1298,6 +1358,11 @@
           <t>302</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 2, 3, 4A1, 4A2, 4B1, 4B2, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1305,6 +1370,11 @@
           <t>303</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 13E, 14A, 14B, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1312,6 +1382,11 @@
           <t>304</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1319,6 +1394,11 @@
           <t>305</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 2, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1326,6 +1406,11 @@
           <t>306</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1333,6 +1418,11 @@
           <t>307</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2A, 1D2B, 1E1, 1E2, 2A, 2B, 3A, 3B, 3C, 4A, 4B1, 4B2, 5A, 5B, 6A, 6B, 7A, 7B, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1340,6 +1430,11 @@
           <t>308</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B1, 1B2, 1C1, 1C2, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1347,6 +1442,11 @@
           <t>309</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1354,6 +1454,11 @@
           <t>310</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1361,6 +1466,11 @@
           <t>311</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3A, 3B, 4, 5A, 5B1, 5B10, 5B11, 5B2, 5B3, 5B4, 5B5, 5B6, 5B7, 5B8, 5B9, 5C1, 5C10, 5C11, 5C12, 5C2, 5C3, 5C4, 5C5, 5C6, 5C7, 5C8, 5C9, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1368,6 +1478,11 @@
           <t>312</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1375,6 +1490,11 @@
           <t>313</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1382,6 +1502,11 @@
           <t>314</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 2A, 2B, 2C, 2D, 3A1A, 3A1B, 3A2, 3B, 4, 5A, 5B, 5C, 5D, 5E, 5F, 5G, 5H, 5I, 5J, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1389,6 +1514,11 @@
           <t>315</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 3, 4A, 4B, 4C, 4D, 5A, 5B, 5C, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1396,6 +1526,11 @@
           <t>316</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13A, 13B, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 2, 20, 21, 22, 23, 24, 25A1, 25A2, 25A3, 25B, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 4A, 4B, 4C, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1403,6 +1538,11 @@
           <t>317</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1410,6 +1550,11 @@
           <t>318</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1417,6 +1562,11 @@
           <t>319</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1424,6 +1574,11 @@
           <t>320</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 3, 4, 5, 6A, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1431,6 +1586,11 @@
           <t>321</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1438,6 +1598,11 @@
           <t>322</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1445,6 +1610,11 @@
           <t>323</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1452,6 +1622,11 @@
           <t>324</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 1A, 1B, 2A, 2B, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8A, 8B, 8C, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1459,6 +1634,11 @@
           <t>325</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1466,6 +1646,11 @@
           <t>326</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1473,6 +1658,11 @@
           <t>327</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1480,6 +1670,11 @@
           <t>328</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1487,6 +1682,11 @@
           <t>329</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1494,6 +1694,11 @@
           <t>330</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1501,6 +1706,11 @@
           <t>331</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1508,6 +1718,11 @@
           <t>332</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1515,6 +1730,11 @@
           <t>333</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 5</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1522,6 +1742,11 @@
           <t>334</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1529,6 +1754,11 @@
           <t>335</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1536,6 +1766,11 @@
           <t>336</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1543,6 +1778,11 @@
           <t>337</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1550,6 +1790,11 @@
           <t>338</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1557,6 +1802,11 @@
           <t>339</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1564,6 +1814,11 @@
           <t>340</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1571,6 +1826,11 @@
           <t>341</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1578,6 +1838,11 @@
           <t>342</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12A, 12B, 13, 14, 15, 16, 17A, 17B, 18, 19, 1A, 1B, 1C, 1D, 1E, 1F, 2, 20, 3, 4A, 4B, 4C, 5, 6, 7A, 7B, 7C, 7D, 8A1, 8A2, 8B1, 8B2, 9</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1585,6 +1850,11 @@
           <t>343</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 14, 15, 16, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1592,6 +1862,11 @@
           <t>344</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1599,6 +1874,11 @@
           <t>345</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 2K, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1606,6 +1886,11 @@
           <t>346</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 11, 12, 13, 14, 15A, 15B, 15C, 15D, 16, 17, 18, 19A1, 19A2, 19B, 2, 20, 21, 22, 3, 4, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1613,6 +1898,11 @@
           <t>347</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12A, 12B, 13, 14, 15A, 15B, 15C, 15D, 15E, 15F, 15G, 15H, 15I, 15J, 15K, 16, 17, 18A, 18B1, 18B2, 18C, 18D, 1A, 1B, 1C, 1D1, 1D2, 1E, 1F1, 1F2, 1G, 1H, 1I, 1J, 1K, 2A, 2B, 3, 4, 5A, 5B, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1620,6 +1910,11 @@
           <t>348</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C1, 1C2, 1C3, 1D, 1E, 1F, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1627,6 +1922,11 @@
           <t>349</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21, 22, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1634,6 +1934,11 @@
           <t>350</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 35, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1641,6 +1946,11 @@
           <t>351</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 14, 15, 16, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1648,6 +1958,11 @@
           <t>352</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11A, 11B, 12A, 12B, 12C, 12D, 12E, 12F, 12G, 13, 14A, 14B, 14C, 15, 16, 17, 18A, 18B, 18C, 18D, 19A, 19B, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1, 2A2, 2B, 3, 30, 31, 32, 33, 34, 35A, 35B, 36, 37, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1655,6 +1970,11 @@
           <t>353</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18A, 18B, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1662,6 +1982,11 @@
           <t>354</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 15C, 15D, 16A, 16B, 16C, 16D1, 16D2, 16E, 16F, 16G, 16H, 17, 18, 19A, 19B, 19C, 19D, 2, 20, 21, 22, 23A, 23B, 23C, 3, 4, 5, 6A, 6B, 7, 8A, 8B, 8C, 9A, 9B, 9C1, 9C2, 9D, 9E</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1669,6 +1994,11 @@
           <t>355</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1676,6 +2006,11 @@
           <t>356</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25A, 25B, 26, 27, 28, 29, 3, 30, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1683,6 +2018,11 @@
           <t>357</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1690,6 +2030,11 @@
           <t>358</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1697,6 +2042,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 21C, 22, 23, 24, 25, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1704,6 +2054,11 @@
           <t>360</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A1, 17A2, 17B, 18, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1711,6 +2066,11 @@
           <t>361</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1718,6 +2078,11 @@
           <t>362</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1725,6 +2090,11 @@
           <t>363</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1732,6 +2102,11 @@
           <t>364</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 12E, 13, 14A, 14B, 14C, 15, 16, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1739,6 +2114,11 @@
           <t>365</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A1, 12A2, 12A3, 12B, 12C1, 12C2, 12C3, 12D, 12E, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 2A, 2B, 3, 4, 5, 6A1, 6A2, 6A3, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1746,6 +2126,11 @@
           <t>366</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12A, 12B, 13, 14A, 14B, 15A, 15B, 16A, 16B, 16C, 16D1, 16D2, 17A, 17B, 17C, 18, 19, 2, 20, 3A, 3B, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 5, 6A, 6B, 7, 8, 9A1, 9A2, 9B, 9C, 9D, 9E, 9F</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1753,6 +2138,11 @@
           <t>367</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3, 4, 5A, 5B, 6A, 6B1A1, 6B1A2, 6B1B, 6B2, 6C1, 6C2, 6C3, 6D, 6E1, 6E2, 6F1, 6F2, 6F3, 6F4, 6F5, 6G, 7A, 7B, 7C1, 7C2, 7D</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1760,6 +2150,11 @@
           <t>368</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E1, 1E2, 1E3, 2A, 2B, 2C1, 2C2, 2D1, 2D2, 3A, 3B1, 3B2, 4A1, 4A2, 4B, 4C1, 4C2, 4D, 4E1A1, 4E1A2, 4E1B, 4E2</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1767,6 +2162,11 @@
           <t>369</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C1, 2C2, 3A, 3B, 4, 5A, 5B, 6A, 6B, 7A, 7B, 7C</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1774,6 +2174,11 @@
           <t>370</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A1, 3A2, 3A3, 3A4, 3A5, 3A6, 3B, 4A, 4B, 5A, 5B, 5C, 5D, 5E, 6A1, 6A2, 6B, 7A1, 7A2, 7B1, 7B2, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1781,6 +2186,11 @@
           <t>371</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3A, 3B, 3C, 4, 5, 6A1A1, 6A1A2, 6A1B, 6A2, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1788,6 +2198,11 @@
           <t>372</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>10A1, 10A2, 10B, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1795,6 +2210,11 @@
           <t>373</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1802,6 +2222,11 @@
           <t>374</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 2A, 2B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1809,6 +2234,11 @@
           <t>375</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9A, 9B1, 9B2</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1816,6 +2246,11 @@
           <t>376</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1823,11 +2258,21 @@
           <t>377</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
           <t>378</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22A, 22B, 23, 24, 25, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 4, 5A, 5B, 6, 7, 8A, 8B, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
@@ -2282,6 +2282,11 @@
           <t>379</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 3, 4, 5A, 5B, 6, 7, 8, 9A, 9B, 9C, 9D</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2289,6 +2294,11 @@
           <t>380</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2296,6 +2306,11 @@
           <t>381</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2303,6 +2318,11 @@
           <t>382</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2A, 2B, 2C, 3A, 3B, 3C, 4A, 4B, 4C, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2310,6 +2330,11 @@
           <t>383</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2317,6 +2342,11 @@
           <t>384</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 3A, 3B, 3C1, 3C2, 3C3</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2324,6 +2354,11 @@
           <t>385</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18A, 18B, 19, 2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2331,6 +2366,11 @@
           <t>386</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2338,6 +2378,11 @@
           <t>387</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 19, 2, 20A, 20B, 20C, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2345,6 +2390,11 @@
           <t>388</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2352,6 +2402,11 @@
           <t>389</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2359,6 +2414,11 @@
           <t>390</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24A, 24B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2366,6 +2426,11 @@
           <t>391</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 11C, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2373,6 +2438,11 @@
           <t>392</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2380,6 +2450,11 @@
           <t>393</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2387,6 +2462,11 @@
           <t>394</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 12C, 12D, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 23, 24, 25, 26A, 26B, 26C, 27A, 27B, 27C, 27D, 28, 29, 2A, 2B, 30, 31, 32, 33, 34, 35, 36, 37, 3A, 3B, 3C, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2394,6 +2474,11 @@
           <t>395</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 13C, 13D, 14, 15A, 15B, 16A, 16B, 16C, 17, 18A, 18B, 19A, 19B, 19C, 2, 20A, 20B, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2401,6 +2486,11 @@
           <t>396</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2408,6 +2498,11 @@
           <t>397</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2415,6 +2510,11 @@
           <t>398</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1, 4A2, 4B1, 4B2, 4B3, 5</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2422,6 +2522,11 @@
           <t>399</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A1A1, 2A1A2, 2A1A3, 2A1B, 2A2A, 2A2B, 2A2C, 2A2D1, 2A2D2, 2B, 3A1, 3A2, 3A3, 3A4A, 3A4B, 3A4C, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2429,6 +2534,11 @@
           <t>400</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 2, 3A, 3B, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2436,6 +2546,11 @@
           <t>401</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B1, 3B2, 3B3, 3B4, 3B5</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2443,6 +2558,11 @@
           <t>402</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2450,6 +2570,11 @@
           <t>403</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2457,6 +2582,11 @@
           <t>404</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2464,6 +2594,11 @@
           <t>405</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 1A, 1B1, 1B2, 1B3, 2A, 2B, 2C, 3A, 3B, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2471,6 +2606,11 @@
           <t>406</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2478,6 +2618,11 @@
           <t>407</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17A, 17B, 17C, 17D, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2485,6 +2630,11 @@
           <t>408</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 13, 14, 2, 3, 4A1, 4A2, 4B1, 4B2, 5, 6A, 6B, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2492,6 +2642,11 @@
           <t>409</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A1A1, 14A2, 14B1A1, 14B2, 15, 16A, 16B, 17A, 17B, 18, 19, 2A, 2B, 3A, 3B, 4, 5, 6, 7A, 7B, 7C1, 7C2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2499,6 +2654,11 @@
           <t>410</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11A, 11B, 12A, 12B, 13, 14, 16, 17A, 18, 19, 2A1, 2A2, 2B, 3A, 3B1, 3B2, 3B3, 3C1A1, 3C1A2, 3C1A3, 3C1B, 3C2, 3D1A, 3D1A2, 3D1B, 3D2, 4A, 4B, 5A, 5B, 6, 7, 8, 9A1, 9A2, 9B1, 9B2, 9C1A, 9C1B, 9C2</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2506,6 +2666,11 @@
           <t>411</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2513,6 +2678,11 @@
           <t>412</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2A, 1D2B, 2A, 2B, 2C, 2D, 2E</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2520,6 +2690,11 @@
           <t>413</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2527,6 +2702,11 @@
           <t>414</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2534,6 +2714,11 @@
           <t>415</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 3E, 4</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2541,6 +2726,11 @@
           <t>416</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1, 10, 11A1, 11A2, 11B, 11C, 12A1, 12A2A, 12A2B, 12B1, 12B2A, 12B2B, 12B2C, 13A, 13B, 14A1A1A1, 14A1B, 14A2, 14B, 15A, 15B, 16A, 16B1, 16B2, 16C, 17, 18, 19, 2, 20, 21A, 21B, 22A1, 22A2, 22B, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A, 3B, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 5A1A, 5A1B, 5A2, 5B1, 5B2, 5C1, 5C2, 60, 61, 62, 63, 64, 6A1, 6A2, 6B1A1, 6B2, 6B3, 6B4, 6B5A1, 7A1, 7A2, 7B1A1A, 7B2A1, 7B2A2, 7B3, 8A1, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2548,6 +2738,11 @@
           <t>417</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 2A, 2B, 2C, 2D, 3A, 3B, 3C, 4A1A1A1A, 4A1B, 4A2A1, 4A2B, 4A3A, 4A3B, 4B, 5A1A, 5A2A, 5A2B, 5A3, 5B1, 5B2A, 5B2B, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2555,6 +2750,11 @@
           <t>418</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2562,6 +2762,11 @@
           <t>419</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2569,6 +2774,11 @@
           <t>420</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3A1, 1A3A2, 1A3B, 1A4A1, 1A4A2, 1A4B, 1B1, 1B2, 1B3A, 1B3B, 1B3C, 1B4, 1B5A, 1B5B, 1C1, 1C2, 2A, 2B, 3A1, 3A2, 3B1A, 3B1B, 3B2, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2576,6 +2786,11 @@
           <t>421</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 1B, 29, 2A, 2B1A, 2B1B, 2B2, 2C, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 6, 7, 9</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2583,6 +2798,11 @@
           <t>422</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5A, 5B1, 5B2, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2590,6 +2810,11 @@
           <t>423</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2597,6 +2822,11 @@
           <t>424</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2604,6 +2834,11 @@
           <t>425</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2611,11 +2846,21 @@
           <t>426</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B1, 14B2, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
           <t>427</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7, 8A, 8B</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
@@ -2618,6 +2618,11 @@
           <t>407</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17A, 17B, 17C, 17D, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2625,6 +2630,11 @@
           <t>408</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 13, 14, 2, 3, 4A1, 4A2, 4B1, 4B2, 5, 6A, 6B, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2632,11 +2642,21 @@
           <t>409</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A1A1, 14A2, 14B1A1, 14B2, 15, 16A, 16B, 17A, 17B, 18, 19, 2A, 2B, 3A, 3B, 4, 5, 6, 7A, 7B, 7C1, 7C2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
           <t>410</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11A, 11B, 12A, 12B, 13, 14, 16, 17A, 18, 19, 2A1, 2A2, 2B, 3A, 3B1, 3B2, 3B3, 3C1A1, 3C1A2, 3C1A3, 3C1B, 3C2, 3D1A, 3D1A2, 3D1B, 3D2, 4A, 4B, 5A, 5B, 6, 7, 8, 9A1, 9A2, 9B1, 9B2, 9C1A, 9C1B, 9C2</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Melpakkam_13.447249_80.074836.xlsx
@@ -2666,6 +2666,11 @@
           <t>411</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2673,6 +2678,11 @@
           <t>412</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2A, 1D2B, 2A, 2B, 2C, 2D, 2E</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2680,6 +2690,11 @@
           <t>413</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2687,6 +2702,11 @@
           <t>414</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2694,6 +2714,11 @@
           <t>415</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 3E, 4</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2701,6 +2726,11 @@
           <t>416</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1, 10, 11A1, 11A2, 11B, 11C, 12A1, 12A2A, 12A2B, 12B1, 12B2A, 12B2B, 12B2C, 13A, 13B, 14A1A1A1, 14A1B, 14A2, 14B, 15A, 15B, 16A, 16B1, 16B2, 16C, 17, 18, 19, 2, 20, 21A, 21B, 22A1, 22A2, 22B, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A, 3B, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 5A1A, 5A1B, 5A2, 5B1, 5B2, 5C1, 5C2, 60, 61, 62, 63, 64, 6A1, 6A2, 6B1A1, 6B2, 6B3, 6B4, 6B5A1, 7A1, 7A2, 7B1A1A, 7B2A1, 7B2A2, 7B3, 8A1, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2708,6 +2738,11 @@
           <t>417</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 2A, 2B, 2C, 2D, 3A, 3B, 3C, 4A1A1A1A, 4A1B, 4A2A1, 4A2B, 4A3A, 4A3B, 4B, 5A1A, 5A2A, 5A2B, 5A3, 5B1, 5B2A, 5B2B, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2715,6 +2750,11 @@
           <t>418</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2722,6 +2762,11 @@
           <t>419</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2729,6 +2774,11 @@
           <t>420</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3A1, 1A3A2, 1A3B, 1A4A1, 1A4A2, 1A4B, 1B1, 1B2, 1B3A, 1B3B, 1B3C, 1B4, 1B5A, 1B5B, 1C1, 1C2, 2A, 2B, 3A1, 3A2, 3B1A, 3B1B, 3B2, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2736,6 +2786,11 @@
           <t>421</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 1B, 29, 2A, 2B1A, 2B1B, 2B2, 2C, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 6, 7, 9</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2743,6 +2798,11 @@
           <t>422</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5A, 5B1, 5B2, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2750,6 +2810,11 @@
           <t>423</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2757,6 +2822,11 @@
           <t>424</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2764,6 +2834,11 @@
           <t>425</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2771,11 +2846,21 @@
           <t>426</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B1, 14B2, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
           <t>427</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7, 8A, 8B</t>
         </is>
       </c>
     </row>
